--- a/docs/oc-mensuales/suministro-de-combustibles/oct-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M610"/>
+  <dimension ref="A1:M611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30674,7 +30674,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2660-77-CM26</t>
+          <t>4197-254-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30699,12 +30699,12 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>69.230.200-1</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE QUEMCHI</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -30714,17 +30714,17 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -30733,7 +30733,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>42785.11</v>
+        <v>5093.47</v>
       </c>
     </row>
     <row r="467">
@@ -31259,7 +31259,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>4197-254-CM26</t>
+          <t>2660-77-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -31284,12 +31284,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>69.230.200-1</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUEMCHI</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -31299,17 +31299,17 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -31318,7 +31318,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>5093.47</v>
+        <v>42785.11</v>
       </c>
     </row>
     <row r="476">
@@ -31974,7 +31974,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2918-52-CM26</t>
+          <t>3760-391-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -31999,17 +31999,17 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.073.000-6</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE EL MONTE</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -32033,7 +32033,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>6009</v>
+        <v>5092.38</v>
       </c>
     </row>
     <row r="487">
@@ -32104,7 +32104,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>5690-172-CM26</t>
+          <t>1199-238-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -32129,17 +32129,17 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -32163,13 +32163,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>18332.55</v>
+        <v>2240.65</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>1199-238-CM26</t>
+          <t>3892-546-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32194,17 +32194,17 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -32228,13 +32228,13 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>2240.65</v>
+        <v>2546.19</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>3892-546-CM26</t>
+          <t>2906-144-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -32254,22 +32254,22 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -32293,13 +32293,13 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>2546.19</v>
+        <v>15277.13</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2906-144-CM26</t>
+          <t>2918-52-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -32319,22 +32319,22 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -32358,13 +32358,13 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>15277.13</v>
+        <v>6009</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>3760-391-CM26</t>
+          <t>1389585-222-CM26</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -32384,17 +32384,17 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>69.073.000-6</t>
+          <t>70.882.100-4</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL MONTE</t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -32423,7 +32423,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>5092.38</v>
+        <v>2240.65</v>
       </c>
     </row>
     <row r="493">
@@ -32494,7 +32494,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>934-200-CM26</t>
+          <t>4484-143-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -32514,22 +32514,22 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -32553,13 +32553,13 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>3055.43</v>
+        <v>6110.85</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>4484-143-CM26</t>
+          <t>3876-195-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -32584,17 +32584,17 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>6110.85</v>
+        <v>4073.9</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>3876-195-CM26</t>
+          <t>3177-347-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32644,37 +32644,37 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -32683,7 +32683,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>4073.9</v>
+        <v>2398.16</v>
       </c>
     </row>
     <row r="497">
@@ -32949,7 +32949,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>3177-347-CM26</t>
+          <t>934-200-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32974,32 +32974,32 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -33008,13 +33008,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>2398.16</v>
+        <v>3055.43</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1389585-222-CM26</t>
+          <t>4474-1011-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -33034,22 +33034,22 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>70.882.100-4</t>
+          <t>69.160.600-7</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -33073,13 +33073,13 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2240.65</v>
+        <v>3055.43</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>4474-1011-CM26</t>
+          <t>5690-172-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -33104,17 +33104,17 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>69.160.600-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -33138,13 +33138,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>3055.43</v>
+        <v>18332.55</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2002-49-CM26</t>
+          <t>3146-70-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -33164,22 +33164,22 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>60.103.005-5</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -33203,13 +33203,13 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>3564.66</v>
+        <v>3055.43</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>3146-70-CM26</t>
+          <t>4474-1010-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -33234,17 +33234,17 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.160.600-7</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -33268,13 +33268,13 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>3055.43</v>
+        <v>5092.38</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>4474-1010-CM26</t>
+          <t>5297-43-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -33299,12 +33299,12 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>69.160.600-7</t>
+          <t>61.102.156-9</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -33333,13 +33333,13 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>5092.38</v>
+        <v>3055.43</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>5297-43-CM26</t>
+          <t>3759-1008-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33364,17 +33364,17 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>61.102.156-9</t>
+          <t>69.130.400-0</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>3055.43</v>
+        <v>11203.23</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>3759-1008-CM26</t>
+          <t>1409-83-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33429,17 +33429,17 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>69.130.400-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -33463,13 +33463,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>11203.23</v>
+        <v>3381.61</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>1409-83-CM26</t>
+          <t>3799-348-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -33494,17 +33494,17 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -33528,13 +33528,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>3381.61</v>
+        <v>13240.18</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>3799-348-CM26</t>
+          <t>2125-2046-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33554,22 +33554,22 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -33593,7 +33593,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>13240.18</v>
+        <v>6110.85</v>
       </c>
     </row>
     <row r="511">
@@ -33729,7 +33729,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2125-2046-CM26</t>
+          <t>2002-49-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33754,17 +33754,17 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>60.103.005-5</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -33788,7 +33788,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>6110.85</v>
+        <v>3564.66</v>
       </c>
     </row>
     <row r="514">
@@ -34314,7 +34314,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>3335-1467-CM26</t>
+          <t>656-211-CM26</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -34339,32 +34339,32 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.818.001-8</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -34373,13 +34373,13 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>4324.46</v>
+        <v>3065.73</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>656-211-CM26</t>
+          <t>2151-408-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -34404,17 +34404,17 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>61.818.001-8</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -34438,13 +34438,13 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>3065.73</v>
+        <v>2211.95</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2151-408-CM26</t>
+          <t>2151-409-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -34509,7 +34509,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2151-409-CM26</t>
+          <t>4316-70-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34534,17 +34534,17 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -34568,13 +34568,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>2211.95</v>
+        <v>3065.73</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>4316-70-CM26</t>
+          <t>3952-207-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -34599,17 +34599,17 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.091.500-6</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curepto</t>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -34633,13 +34633,13 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>3065.73</v>
+        <v>2554.77</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>3952-207-CM26</t>
+          <t>3335-1467-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34664,32 +34664,32 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -34698,7 +34698,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2554.77</v>
+        <v>4324.46</v>
       </c>
     </row>
     <row r="528">
@@ -34769,7 +34769,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>3888-741-CM26</t>
+          <t>2445-2557-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34794,32 +34794,32 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -34828,7 +34828,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>9193.709999999999</v>
+        <v>5109.55</v>
       </c>
     </row>
     <row r="530">
@@ -34964,7 +34964,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2445-2557-CM26</t>
+          <t>2297-1344-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -34989,32 +34989,32 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -35023,13 +35023,13 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>5109.55</v>
+        <v>5412.25</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2297-1344-CM26</t>
+          <t>1057388-600-CM26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -35054,32 +35054,32 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -35088,13 +35088,13 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>5412.25</v>
+        <v>4087.64</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>1057388-600-CM26</t>
+          <t>1057532-1702-CM26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -35119,32 +35119,32 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -35153,13 +35153,13 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>4087.64</v>
+        <v>5295.92</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>1057532-1702-CM26</t>
+          <t>4660-30-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -35179,37 +35179,37 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
@@ -35218,13 +35218,13 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>5295.92</v>
+        <v>24525.83</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>4660-30-CM26</t>
+          <t>2908-285-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -35244,22 +35244,22 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -35283,7 +35283,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>24525.83</v>
+        <v>2248.2</v>
       </c>
     </row>
     <row r="537">
@@ -35354,7 +35354,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2908-285-CM26</t>
+          <t>3888-741-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -35379,32 +35379,32 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
@@ -35413,13 +35413,13 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>2248.2</v>
+        <v>9193.709999999999</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>1230869-206-CM26</t>
+          <t>2004-41-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -35444,17 +35444,17 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>65.235.450-5</t>
+          <t>60.103.009-8</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Corporación Cultural de La Florida</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -35478,7 +35478,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>2248.2</v>
+        <v>4087.64</v>
       </c>
     </row>
     <row r="540">
@@ -35549,7 +35549,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2004-41-CM26</t>
+          <t>1230869-206-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -35574,17 +35574,17 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>60.103.009-8</t>
+          <t>65.235.450-5</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>Corporación Cultural de La Florida</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -35608,7 +35608,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>4087.64</v>
+        <v>2248.2</v>
       </c>
     </row>
     <row r="542">
@@ -38279,7 +38279,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>807-69-CM26</t>
+          <t>2311-399-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -38304,17 +38304,17 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -38338,13 +38338,13 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>2534.01</v>
+        <v>5574.81</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>1650-452-CM26</t>
+          <t>1274907-573-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -38369,32 +38369,32 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>61.602.204-0</t>
+          <t>71.299.000-7</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>Hospital Santa Juana</t>
+          <t>CORPORACIÓN MUNICIPAL DE EDUCACIÓN, SALUD Y ATENCIÓN DE MENORES CHONCHI</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
@@ -38409,7 +38409,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>1274907-573-CM26</t>
+          <t>1410-996-CM26</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -38434,17 +38434,17 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>71.299.000-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE EDUCACIÓN, SALUD Y ATENCIÓN DE MENORES CHONCHI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -38468,13 +38468,13 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>6081.62</v>
+        <v>8108.82</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>1410-996-CM26</t>
+          <t>807-69-CM26</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -38499,17 +38499,17 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -38533,13 +38533,13 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>8108.82</v>
+        <v>2534.01</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2311-399-CM26</t>
+          <t>2663-668-CM26</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -38564,32 +38564,32 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K587" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L587" t="inlineStr">
@@ -38598,13 +38598,13 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>5574.81</v>
+        <v>8108.82</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>3443-838-CM26</t>
+          <t>5586-3834-CM26</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -38629,17 +38629,17 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -38663,13 +38663,13 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>5191.67</v>
+        <v>3040.81</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>5586-3831-CM26</t>
+          <t>3661-539-CM26</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -38694,17 +38694,17 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -38728,13 +38728,13 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2787.41</v>
+        <v>20272.05</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>3661-539-CM26</t>
+          <t>4134-782-CM26</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -38759,17 +38759,17 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -38793,13 +38793,13 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>20272.05</v>
+        <v>10136.03</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>4134-782-CM26</t>
+          <t>1075963-14089-CM26</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -38824,17 +38824,17 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -38858,13 +38858,13 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>10136.03</v>
+        <v>5014.29</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>1075963-14089-CM26</t>
+          <t>3443-838-CM26</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -38889,17 +38889,17 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -38923,13 +38923,13 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>5014.29</v>
+        <v>5191.67</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>5456-96-CM26</t>
+          <t>1650-452-CM26</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -38949,22 +38949,22 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>65.852.930-7</t>
+          <t>61.602.204-0</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
+          <t>Hospital Santa Juana</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -38988,13 +38988,13 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2971.79</v>
+        <v>6081.62</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2663-668-CM26</t>
+          <t>5586-3831-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -39019,32 +39019,32 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K594" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
@@ -39053,13 +39053,13 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>8108.82</v>
+        <v>2787.41</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2307-1351-CM26</t>
+          <t>5456-96-CM26</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -39079,22 +39079,22 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>65.852.930-7</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL RANCO</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -39118,7 +39118,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>4799.97</v>
+        <v>2971.79</v>
       </c>
     </row>
     <row r="596">
@@ -39189,7 +39189,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>3332-119-CM26</t>
+          <t>2137-946-CM26</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -39214,47 +39214,47 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.602.278-4</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
           <t>Atacama</t>
         </is>
       </c>
-      <c r="I597" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J597" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K597" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>2534.01</v>
+        <v>3040.81</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2989-604-CM26</t>
+          <t>3332-119-CM26</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -39279,17 +39279,17 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -39313,13 +39313,13 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>10136.03</v>
+        <v>2534.01</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1162-173-CM26</t>
+          <t>2989-604-CM26</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -39344,17 +39344,17 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -39378,13 +39378,13 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>14743.65</v>
+        <v>10136.03</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>4157-1038-CM26</t>
+          <t>1162-173-CM26</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -39409,17 +39409,17 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -39443,13 +39443,13 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>2534.01</v>
+        <v>14743.65</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>707427-56-CM26</t>
+          <t>4157-1038-CM26</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -39474,17 +39474,17 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -39508,13 +39508,13 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>2229.93</v>
+        <v>2534.01</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1067355-508-CM26</t>
+          <t>707427-56-CM26</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -39539,32 +39539,32 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K602" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
@@ -39573,13 +39573,13 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>3547.61</v>
+        <v>2229.93</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>1407-652-CM26</t>
+          <t>1067355-508-CM26</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -39604,32 +39604,32 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -39638,13 +39638,13 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>12163.23</v>
+        <v>3547.61</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>948354-1653-CM26</t>
+          <t>1407-652-CM26</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -39669,27 +39669,27 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K604" t="inlineStr">
@@ -39703,13 +39703,13 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>15204.04</v>
+        <v>12163.23</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2626-505-CM26</t>
+          <t>948354-1653-CM26</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -39734,17 +39734,17 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -39768,13 +39768,13 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>4713.25</v>
+        <v>15204.04</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2307-1294-CM26</t>
+          <t>2626-505-CM26</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -39799,32 +39799,32 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -39833,13 +39833,13 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>3554.34</v>
+        <v>4713.25</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>4295-93-CM26</t>
+          <t>2307-1294-CM26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -39864,32 +39864,32 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
@@ -39898,13 +39898,13 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>243264.61</v>
+        <v>3554.34</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>5586-3834-CM26</t>
+          <t>4295-93-CM26</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -39929,17 +39929,17 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -39963,13 +39963,13 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>3040.81</v>
+        <v>243264.61</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2137-946-CM26</t>
+          <t>1057384-865-CM26</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -39994,32 +39994,32 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>61.602.278-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K609" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
@@ -40028,13 +40028,13 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>3040.81</v>
+        <v>4054.41</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>1057384-865-CM26</t>
+          <t>2307-1351-CM26</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -40059,32 +40059,32 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
@@ -40093,7 +40093,72 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>4054.41</v>
+        <v>4799.97</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2035-50-CM26</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>60.511.032-0</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M611" s="2" t="n">
+        <v>3040.81</v>
       </c>
     </row>
   </sheetData>
